--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486744_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486744_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0667</v>
+        <v>2.984</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1566</v>
+        <v>4.9497</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0899</v>
+        <v>-1.9657</v>
       </c>
       <c r="G2" t="n">
         <v>2.9785</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1654</v>
+        <v>0.0827</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0476</v>
+        <v>0.8408</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8823</v>
+        <v>-0.7581</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6565</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8626</v>
+        <v>1.1258</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0858</v>
+        <v>5.4715</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2232</v>
+        <v>-4.3456</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9012</v>
+        <v>3.14</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8967</v>
+        <v>3.6622</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0045</v>
+        <v>-0.5222</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6404</v>
+        <v>5.5958</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5183</v>
+        <v>4.9041</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1221</v>
+        <v>0.6918</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.7392</v>
+        <v>-2.4558</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.6216</v>
+        <v>-1.2418</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1176</v>
+        <v>-1.214</v>
       </c>
       <c r="P3" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.5929</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-2.4554</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.9308</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.9308</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.2744</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.0753</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1991</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-1.3129</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.6991000000000001</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.6138</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.716</v>
+        <v>0.9193</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0368</v>
+        <v>2.4653</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.3208</v>
+        <v>-1.546</v>
       </c>
       <c r="G4" t="n">
-        <v>3.14</v>
+        <v>1.9012</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6622</v>
+        <v>1.8967</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5222</v>
+        <v>0.0045</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5958</v>
+        <v>4.6404</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9041</v>
+        <v>4.5183</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6918</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4558</v>
+        <v>-2.7392</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2418</v>
+        <v>-2.6216</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.214</v>
+        <v>-0.1176</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1585</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8384</v>
+        <v>0.331</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4064</v>
+        <v>0.4547</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.1237</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4554</v>
+        <v>-1.3129</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4554</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.308</v>
+        <v>0.8502</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6235</v>
+        <v>5.265</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.3154</v>
+        <v>-4.4148</v>
       </c>
       <c r="G5" t="n">
         <v>2.4076</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>0.182</v>
+        <v>-0.2758</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3859</v>
+        <v>0.0274</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2039</v>
+        <v>-0.3032</v>
       </c>
       <c r="V5" t="n">
         <v>-2.8262</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.0344</v>
+        <v>-2.7242</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1927</v>
+        <v>-1.8825</v>
       </c>
       <c r="F6" t="n">
         <v>-0.8417</v>
@@ -922,10 +922,10 @@
         <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3862</v>
+        <v>0.6964</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1102</v>
+        <v>0.4205</v>
       </c>
       <c r="U6" t="n">
         <v>0.2759</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.147</v>
+        <v>-2.8119</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6705</v>
+        <v>-1.3602</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4765</v>
+        <v>-1.4517</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7872</v>
@@ -1000,13 +1000,13 @@
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2592</v>
+        <v>0.0759</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1378</v>
+        <v>0.448</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.397</v>
+        <v>-0.3722</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9421</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.5919</v>
+        <v>-4.4333</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.011</v>
+        <v>-0.8524</v>
       </c>
       <c r="F8" t="n">
         <v>-3.5809</v>
@@ -1078,10 +1078,10 @@
         <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2483</v>
+        <v>-0.0897</v>
       </c>
       <c r="T8" t="n">
-        <v>0.303</v>
+        <v>0.4616</v>
       </c>
       <c r="U8" t="n">
         <v>-0.5512</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9922</v>
+        <v>-4.5026</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5014</v>
+        <v>-2.1359</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4908</v>
+        <v>-2.3666</v>
       </c>
       <c r="G9" t="n">
         <v>-2.485</v>
@@ -1156,13 +1156,13 @@
         <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8274</v>
+        <v>-0.3378</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3587</v>
+        <v>0.0067</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4687</v>
+        <v>-0.3445</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3282</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.4612</v>
+        <v>-6.4048</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1797</v>
+        <v>-2.2971</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2815</v>
+        <v>-4.1077</v>
       </c>
       <c r="G10" t="n">
         <v>-6.6321</v>
@@ -1234,13 +1234,13 @@
         <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3737</v>
+        <v>-0.3173</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3865</v>
+        <v>0.496</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9872</v>
+        <v>-0.8133</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.2734</v>
+        <v>-14.9975</v>
       </c>
       <c r="E11" t="n">
-        <v>9.3474</v>
+        <v>9.623399999999998</v>
       </c>
       <c r="F11" t="n">
         <v>-24.6207</v>
@@ -1279,7 +1279,7 @@
         <v>-5.4835</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3805</v>
+        <v>-1.380499999999998</v>
       </c>
       <c r="I11" t="n">
         <v>-4.1029</v>
@@ -1291,7 +1291,7 @@
         <v>17.9368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5204000000000004</v>
+        <v>0.5203999999999995</v>
       </c>
       <c r="M11" t="n">
         <v>-23.9405</v>
@@ -1312,13 +1312,13 @@
         <v>14.4809</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1377999999999999</v>
+        <v>0.4136</v>
       </c>
       <c r="T11" t="n">
-        <v>3.721</v>
+        <v>3.9967</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.5833</v>
+        <v>-3.5832</v>
       </c>
       <c r="V11" t="n">
         <v>-6.065799999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2742</v>
+        <v>8.975</v>
       </c>
       <c r="E12" t="n">
-        <v>8.642200000000001</v>
+        <v>7.9183</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6319</v>
+        <v>1.0567</v>
       </c>
       <c r="G12" t="n">
         <v>0.662</v>
@@ -1390,13 +1390,13 @@
         <v>2.51</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8439</v>
+        <v>0.5447</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7097</v>
+        <v>0.9857</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8658</v>
+        <v>-0.441</v>
       </c>
       <c r="V12" t="n">
         <v>6.2237</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6586</v>
+        <v>6.3592</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7563</v>
+        <v>5.8252</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0976</v>
+        <v>0.534</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8589</v>
+        <v>4.0214</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6276</v>
+        <v>0.6486</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7687</v>
+        <v>3.3729</v>
       </c>
       <c r="J13" t="n">
-        <v>3.86</v>
+        <v>5.9328</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6973</v>
+        <v>2.7181</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1628</v>
+        <v>3.2147</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.0011</v>
+        <v>-1.9113</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0697</v>
+        <v>-2.0695</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9314</v>
+        <v>0.1582</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>2.51</v>
+        <v>2.7031</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6992</v>
+        <v>-0.0138</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4063</v>
+        <v>-0.0417</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2929</v>
+        <v>0.0279</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5559</v>
+        <v>0.6138</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4554</v>
+        <v>0.8995</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8995</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4243</v>
+        <v>4.5663</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2047</v>
+        <v>5.7221</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2197</v>
+        <v>-1.1558</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0214</v>
+        <v>0.8589</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6486</v>
+        <v>1.6276</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3729</v>
+        <v>-0.7687</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9328</v>
+        <v>3.86</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7181</v>
+        <v>3.6973</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2147</v>
+        <v>0.1628</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9113</v>
+        <v>-3.0011</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0695</v>
+        <v>-2.0697</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1582</v>
+        <v>-0.9314</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7031</v>
+        <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9487</v>
+        <v>0.6069</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6622</v>
+        <v>0.372</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2865</v>
+        <v>0.2348</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6138</v>
+        <v>1.5559</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8995</v>
+        <v>2.4554</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2856</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. OMERAGIC ALIC</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0086</v>
+        <v>3.9416</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9005</v>
+        <v>3.7993</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.892</v>
+        <v>0.1423</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6834</v>
+        <v>1.5844</v>
       </c>
       <c r="H15" t="n">
-        <v>0.269</v>
+        <v>0.2619</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4144</v>
+        <v>1.3225</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0565</v>
+        <v>3.8406</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0626</v>
+        <v>2.1247</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9939</v>
+        <v>1.7159</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3731</v>
+        <v>-2.2562</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7936</v>
+        <v>-1.8628</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4205</v>
+        <v>-0.3934</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3019</v>
+        <v>0.1448</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2961</v>
+        <v>0.048</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0058</v>
+        <v>0.0968</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9421</v>
+        <v>2.2124</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5133</v>
+        <v>1.8415</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4554</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>A. OMERAGIC ALIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1239</v>
+        <v>3.7962</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2822</v>
+        <v>5.4868</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1583</v>
+        <v>-1.6907</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5844</v>
+        <v>2.6834</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2619</v>
+        <v>0.269</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3225</v>
+        <v>2.4144</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8406</v>
+        <v>4.0565</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1247</v>
+        <v>2.0626</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7159</v>
+        <v>1.9939</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2562</v>
+        <v>-1.3731</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8628</v>
+        <v>-1.7936</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3934</v>
+        <v>0.4205</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6729000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4691</v>
+        <v>0.8824</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2038</v>
+        <v>0.2071</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2124</v>
+        <v>-0.9421</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8415</v>
+        <v>1.5133</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3709</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2891</v>
+        <v>1.7083</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8744</v>
+        <v>2.0812</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5853</v>
+        <v>-0.3729</v>
       </c>
       <c r="G17" t="n">
         <v>1.5152</v>
@@ -1780,13 +1780,13 @@
         <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4192</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1104</v>
+        <v>0.0965</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3088</v>
+        <v>-0.0965</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1311</v>
+        <v>-1.4876</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4081</v>
+        <v>0.861</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.723</v>
+        <v>-2.3486</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4537</v>
+        <v>-1.1672</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5034</v>
+        <v>-0.4347</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0497</v>
+        <v>-0.7325</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7228</v>
+        <v>0.544</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6415</v>
+        <v>1.1521</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0814</v>
+        <v>-0.6081</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2692</v>
+        <v>-1.7112</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1381</v>
+        <v>-1.5868</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1311</v>
+        <v>-0.1244</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3917</v>
+        <v>0.4551</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1655</v>
+        <v>0.317</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2261</v>
+        <v>0.1381</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>-2.1271</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.384</v>
+        <v>-1.6774</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2405</v>
+        <v>-0.3047</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6244</v>
+        <v>-1.3727</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1672</v>
+        <v>0.4537</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4347</v>
+        <v>0.5034</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7325</v>
+        <v>-0.0497</v>
       </c>
       <c r="J19" t="n">
-        <v>0.544</v>
+        <v>0.7228</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1521</v>
+        <v>0.6415</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6081</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7112</v>
+        <v>-0.2692</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5868</v>
+        <v>-0.1381</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1244</v>
+        <v>-0.1311</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.3515</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.4412</v>
+        <v>0.062</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3036</v>
+        <v>-0.0621</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1377</v>
+        <v>0.1242</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1271</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1271</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5233</v>
+        <v>-2.1126</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.408</v>
+        <v>-1.2623</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1154</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7534</v>
+        <v>-1.8697</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9585</v>
+        <v>-2.055</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7949</v>
+        <v>0.1854</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8007</v>
+        <v>-0.2209</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1456</v>
+        <v>-0.2616</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9464</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9527</v>
+        <v>-1.6488</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1041</v>
+        <v>-1.7934</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1514</v>
+        <v>0.1447</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>1.037</v>
+        <v>-0.2276</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7097</v>
+        <v>-0.076</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6727</v>
+        <v>-0.1516</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6138</v>
+        <v>0.3709</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6353</v>
+        <v>-2.5739</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5726</v>
+        <v>-3.2709</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0627</v>
+        <v>0.697</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8697</v>
+        <v>-0.5052</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.055</v>
+        <v>-0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1854</v>
+        <v>-0.1402</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2209</v>
+        <v>1.0681</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2616</v>
+        <v>1.6355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>-0.5674</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6488</v>
+        <v>-1.5733</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7934</v>
+        <v>-2.0005</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1447</v>
+        <v>0.4272</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3862</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7503</v>
+        <v>-0.1379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3863</v>
+        <v>0.1791</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.364</v>
+        <v>-0.317</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3709</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8316</v>
+        <v>-2.7743</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8914</v>
+        <v>-2.2354</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0598</v>
+        <v>-0.5389</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5052</v>
+        <v>-2.7534</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.365</v>
+        <v>-0.9585</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1402</v>
+        <v>-1.7949</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0681</v>
+        <v>-1.8007</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6355</v>
+        <v>0.1456</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5674</v>
+        <v>-1.9464</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5733</v>
+        <v>-0.9527</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0005</v>
+        <v>-1.1041</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4272</v>
+        <v>0.1514</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.1931</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.9308</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.8616</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3956</v>
+        <v>0.786</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4415</v>
+        <v>0.8823</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9542</v>
+        <v>-0.0963</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6565</v>
+        <v>0.6138</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>15.2734</v>
+        <v>18.7208</v>
       </c>
       <c r="E23" t="n">
-        <v>24.6207</v>
+        <v>24.6206</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.347300000000001</v>
+        <v>-5.8999</v>
       </c>
       <c r="G23" t="n">
         <v>5.483499999999998</v>
@@ -2239,7 +2239,7 @@
         <v>-0.5203</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8614</v>
+        <v>3.861400000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.481</v>
@@ -2248,16 +2248,16 @@
         <v>18.3424</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1375999999999997</v>
+        <v>3.3097</v>
       </c>
       <c r="T23" t="n">
         <v>3.5832</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.7209</v>
+        <v>-0.2735</v>
       </c>
       <c r="V23" t="n">
-        <v>6.065999999999999</v>
+        <v>6.066</v>
       </c>
       <c r="W23" t="n">
         <v>11.5778</v>
